--- a/每日板块信息自动化分析报告/每日板块信息.xlsx
+++ b/每日板块信息自动化分析报告/每日板块信息.xlsx
@@ -189,25 +189,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3988.56</v>
+        <v>4055.55</v>
       </c>
       <c r="D2" t="n">
-        <v>2.33</v>
+        <v>28.34</v>
       </c>
       <c r="E2" t="n">
-        <v>0.06</v>
+        <v>0.7</v>
       </c>
       <c r="F2" t="n">
-        <v>19.72</v>
+        <v>86.71</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5</v>
+        <v>2.18</v>
       </c>
       <c r="H2" t="n">
-        <v>-362.28</v>
+        <v>-522.86</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.79</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="3">
@@ -222,25 +222,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9857.4</v>
+        <v>9994.64</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.36</v>
+        <v>49.92</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0</v>
+        <v>0.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-158.46</v>
+        <v>-21.22</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.58</v>
+        <v>-0.21</v>
       </c>
       <c r="H3" t="n">
-        <v>-109.21</v>
+        <v>-371.36</v>
       </c>
       <c r="I3" t="n">
-        <v>-4.02</v>
+        <v>-12.57</v>
       </c>
     </row>
     <row r="4">
@@ -255,25 +255,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2899.47</v>
+        <v>2939.76</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.11</v>
+        <v>5.55</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0</v>
+        <v>0.19</v>
       </c>
       <c r="F4" t="n">
-        <v>-131.66</v>
+        <v>-91.36</v>
       </c>
       <c r="G4" t="n">
-        <v>-4.34</v>
+        <v>-3.01</v>
       </c>
       <c r="H4" t="n">
-        <v>-10.8</v>
+        <v>-300.41</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.88</v>
+        <v>-20.64</v>
       </c>
     </row>
     <row r="5">
@@ -288,25 +288,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4646.15</v>
+        <v>4736.61</v>
       </c>
       <c r="D5" t="n">
-        <v>9.59</v>
+        <v>51.36</v>
       </c>
       <c r="E5" t="n">
-        <v>0.21</v>
+        <v>1.1</v>
       </c>
       <c r="F5" t="n">
-        <v>16.22</v>
+        <v>106.67</v>
       </c>
       <c r="G5" t="n">
-        <v>0.35</v>
+        <v>2.3</v>
       </c>
       <c r="H5" t="n">
-        <v>-690.97</v>
+        <v>-369.39</v>
       </c>
       <c r="I5" t="n">
-        <v>-11.04</v>
+        <v>-6.11</v>
       </c>
     </row>
     <row r="6">
@@ -321,25 +321,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6909.03</v>
+        <v>7068.81</v>
       </c>
       <c r="D6" t="n">
-        <v>-40.35</v>
+        <v>75.55</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.58</v>
+        <v>1.08</v>
       </c>
       <c r="F6" t="n">
-        <v>320.93</v>
+        <v>480.7</v>
       </c>
       <c r="G6" t="n">
-        <v>4.87</v>
+        <v>7.3</v>
       </c>
       <c r="H6" t="n">
-        <v>-98.04</v>
+        <v>-141.43</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.44</v>
+        <v>-5.85</v>
       </c>
     </row>
     <row r="7">
@@ -354,25 +354,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3218.34</v>
+        <v>3237.25</v>
       </c>
       <c r="D7" t="n">
-        <v>7.4</v>
+        <v>6.27</v>
       </c>
       <c r="E7" t="n">
-        <v>0.23</v>
+        <v>0.19</v>
       </c>
       <c r="F7" t="n">
-        <v>180.73</v>
+        <v>199.63</v>
       </c>
       <c r="G7" t="n">
-        <v>5.95</v>
+        <v>6.57</v>
       </c>
       <c r="H7" t="n">
-        <v>24.94</v>
+        <v>-24.15</v>
       </c>
       <c r="I7" t="n">
-        <v>9.42</v>
+        <v>-7.42</v>
       </c>
     </row>
     <row r="8">
@@ -387,25 +387,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5688.09</v>
+        <v>5734.51</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.44</v>
+        <v>13.92</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.08</v>
+        <v>0.24</v>
       </c>
       <c r="F8" t="n">
-        <v>184.11</v>
+        <v>230.53</v>
       </c>
       <c r="G8" t="n">
-        <v>3.34</v>
+        <v>4.19</v>
       </c>
       <c r="H8" t="n">
-        <v>35.14</v>
+        <v>-8.75</v>
       </c>
       <c r="I8" t="n">
-        <v>7.83</v>
+        <v>-1.64</v>
       </c>
     </row>
     <row r="9">
@@ -420,25 +420,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>7967.7</v>
+        <v>8180.08</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.67</v>
+        <v>136.0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02</v>
+        <v>1.69</v>
       </c>
       <c r="F9" t="n">
-        <v>502.12</v>
+        <v>714.51</v>
       </c>
       <c r="G9" t="n">
-        <v>6.73</v>
+        <v>9.57</v>
       </c>
       <c r="H9" t="n">
-        <v>-242.18</v>
+        <v>-269.89</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.58</v>
+        <v>-5.91</v>
       </c>
     </row>
   </sheetData>
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.29</v>
+        <v>16.54</v>
       </c>
       <c r="C2" t="n">
-        <v>15.56</v>
+        <v>15.81</v>
       </c>
       <c r="D2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="E2" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="F2" t="n">
         <v>16.21</v>
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.71</v>
+        <v>12.86</v>
       </c>
       <c r="C3" t="n">
-        <v>12.1</v>
+        <v>12.25</v>
       </c>
       <c r="D3" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="E3" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="F3" t="n">
         <v>13.03</v>
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.88</v>
+        <v>12.0</v>
       </c>
       <c r="C4" t="n">
-        <v>11.54</v>
+        <v>11.68</v>
       </c>
       <c r="D4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="E4" t="n">
-        <v>3.41</v>
+        <v>3.37</v>
       </c>
       <c r="F4" t="n">
         <v>12.33</v>
@@ -584,16 +584,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.1</v>
+        <v>15.33</v>
       </c>
       <c r="C5" t="n">
-        <v>14.22</v>
+        <v>14.45</v>
       </c>
       <c r="D5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="E5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="F5" t="n">
         <v>15.19</v>
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24.75</v>
+        <v>25.26</v>
       </c>
       <c r="C6" t="n">
-        <v>24.19</v>
+        <v>24.65</v>
       </c>
       <c r="D6" t="n">
-        <v>2.15</v>
+        <v>2.19</v>
       </c>
       <c r="E6" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="F6" t="n">
         <v>23.69</v>
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.58</v>
+        <v>8.64</v>
       </c>
       <c r="C7" t="n">
-        <v>8.68</v>
+        <v>8.74</v>
       </c>
       <c r="D7" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="E7" t="n">
-        <v>4.5</v>
+        <v>4.46</v>
       </c>
       <c r="F7" t="n">
         <v>8.62</v>
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.47</v>
+        <v>8.55</v>
       </c>
       <c r="C8" t="n">
-        <v>8.51</v>
+        <v>8.58</v>
       </c>
       <c r="D8" t="n">
         <v>0.76</v>
       </c>
       <c r="E8" t="n">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="F8" t="n">
         <v>8.62</v>
@@ -696,16 +696,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.03</v>
+        <v>30.76</v>
       </c>
       <c r="C9" t="n">
-        <v>28.34</v>
+        <v>28.99</v>
       </c>
       <c r="D9" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="E9" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="F9" t="n">
         <v>28.1</v>
@@ -767,17 +767,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>427.13</t>
+          <t>453.98</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>5.33</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>11.13</t>
         </is>
       </c>
     </row>
@@ -789,22 +789,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>245.25</t>
+          <t>537.50</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>8.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>7.38</t>
         </is>
       </c>
     </row>
@@ -816,22 +816,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>57.75</t>
+          <t>809.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>6.03</t>
         </is>
       </c>
     </row>
@@ -843,22 +843,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>152.30</t>
+          <t>355.57</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>2.13</t>
         </is>
       </c>
     </row>
@@ -870,22 +870,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>立讯精密</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>512.72</t>
+          <t>60.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-1.87</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>-1.78</t>
+          <t>1.56</t>
         </is>
       </c>
     </row>
@@ -897,22 +897,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>恒瑞医药</t>
+          <t>兆易创新</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.20</t>
+          <t>286.73</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.56</t>
         </is>
       </c>
     </row>
@@ -924,22 +924,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>中国巨石</t>
+          <t>蓝思科技</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>25.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>-13.35</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>-1.44</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>寒武纪</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>104.25</t>
+          <t>1307.00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
     </row>
@@ -978,22 +978,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>比亚迪</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1443.31</t>
+          <t>105.54</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>1.25</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>思源电气</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>200.55</t>
+          <t>35.30</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-4.65</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>1.18</t>
         </is>
       </c>
     </row>
@@ -1032,22 +1032,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>天华新能</t>
+          <t>协创数据</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>80.20</t>
+          <t>319.00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>13.65</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>5.49</t>
+          <t>7.36</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1059,22 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>亨通光电</t>
+          <t>大族激光</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>53.49</t>
+          <t>86.67</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>-4.45</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>-3.90</t>
+          <t>5.15</t>
         </is>
       </c>
     </row>
@@ -1086,22 +1086,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>佰维存储</t>
+          <t>厦门钨业</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>255.85</t>
+          <t>61.88</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>5.94</t>
+          <t>10.01</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>3.72</t>
+          <t>4.96</t>
         </is>
       </c>
     </row>
@@ -1113,22 +1113,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>巨人网络</t>
+          <t>长川科技</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>154.09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>-8.80</t>
+          <t>9.12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>4.54</t>
         </is>
       </c>
     </row>
@@ -1140,22 +1140,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>兴森科技</t>
+          <t>天华新能</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>25.23</t>
+          <t>85.68</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9.98</t>
+          <t>11.37</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>4.04</t>
         </is>
       </c>
     </row>
@@ -1167,22 +1167,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中矿资源</t>
+          <t>中钨高新</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>82.92</t>
+          <t>51.90</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.64</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>3.41</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>111.73</t>
+          <t>116.30</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>6.23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>-2.79</t>
+          <t>3.32</t>
         </is>
       </c>
     </row>
@@ -1221,12 +1221,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>恺英网络</t>
+          <t>信立泰</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>18.17</t>
+          <t>60.54</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.74</t>
+          <t>-2.98</t>
         </is>
       </c>
     </row>
@@ -1248,22 +1248,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>菲利华</t>
+          <t>科达利</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>108.90</t>
+          <t>205.59</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>7.67</t>
+          <t>10.00</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.84</t>
         </is>
       </c>
     </row>
@@ -1275,22 +1275,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中材科技</t>
+          <t>中矿资源</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>50.14</t>
+          <t>85.49</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>6.11</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.82</t>
         </is>
       </c>
     </row>
@@ -1302,22 +1302,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>海光信息</t>
+          <t>寒武纪</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>245.25</t>
+          <t>1307.00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4.05</t>
+          <t>2.26</t>
         </is>
       </c>
     </row>
@@ -1329,22 +1329,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>57.75</t>
+          <t>35.30</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>-1.82</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>2.08</t>
         </is>
       </c>
     </row>
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>152.30</t>
+          <t>151.00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3.26</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
@@ -1383,22 +1383,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>恒瑞医药</t>
+          <t>中信证券</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>55.20</t>
+          <t>26.31</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>-2.69</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>
@@ -1415,17 +1415,17 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1443.31</t>
+          <t>1462.84</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0.73</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-2.16</t>
+          <t>-0.95</t>
         </is>
       </c>
     </row>
@@ -1437,22 +1437,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>万华化学</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>92.20</t>
+          <t>105.66</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>-1.10</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>-0.94</t>
         </is>
       </c>
     </row>
@@ -1464,22 +1464,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>中科曙光</t>
+          <t>洛阳钼业</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>88.99</t>
+          <t>20.29</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>0.91</t>
         </is>
       </c>
     </row>
@@ -1491,22 +1491,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>隆基绿能</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>17.68</t>
+          <t>58.52</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.27</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>-0.62</t>
         </is>
       </c>
     </row>
@@ -1518,22 +1518,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>中国太保</t>
+          <t>万华化学</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>37.66</t>
+          <t>90.10</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>-1.08</t>
+          <t>0.62</t>
         </is>
       </c>
     </row>
@@ -1545,22 +1545,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>中微公司</t>
+          <t>金山办公</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>316.58</t>
+          <t>252.46</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>0.61</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>玻璃纤维</t>
+          <t>通信技术服务</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>8.57</t>
+          <t>7.83</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>环境监测</t>
+          <t>钨钼</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.50</t>
+          <t>7.12</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>光伏发电</t>
+          <t>其他发电设备</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.74</t>
+          <t>5.67</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>氨纶及其他化纤</t>
+          <t>云计算服务</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>5.38</t>
+          <t>4.96</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>印制电路板</t>
+          <t>钴镍</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.66</t>
         </is>
       </c>
     </row>
@@ -1684,12 +1684,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>旅游服务</t>
+          <t>制药与生物科技服务</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.95</t>
+          <t>-1.17</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>印染化学品</t>
+          <t>航运</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-4.67</t>
+          <t>-1.10</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>市场服务</t>
+          <t>黑色家电</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.66</t>
+          <t>-1.05</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>培训教育及其他</t>
+          <t>固废处理</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>-1.03</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>休闲设备与用品</t>
+          <t>医药商业</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-1.02</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>玻璃纤维</t>
+          <t>集成电路设计</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>10.56</t>
+          <t>16.51</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>天然气加工</t>
+          <t>市政环卫</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.76</t>
+          <t>7.71</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>其他钢铁</t>
+          <t>摩托车及其他</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6.07</t>
+          <t>7.07</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>云计算服务</t>
+          <t>钨钼</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.19</t>
+          <t>6.98</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>锂</t>
+          <t>其他钢铁</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.11</t>
+          <t>6.76</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>工程机械</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.69</t>
+          <t>-2.29</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>中药饮片</t>
+          <t>药品制剂</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.46</t>
+          <t>-1.46</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>油气开采</t>
+          <t>航天</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-1.15</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>纸制品</t>
+          <t>氨纶及其他化纤</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.96</t>
+          <t>-1.13</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>其他广告营销</t>
+          <t>综合性银行</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.07</t>
         </is>
       </c>
     </row>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>抵押信贷机构</t>
+          <t>其他储能设备</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>10.69</t>
+          <t>50.46</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>印制电路板</t>
+          <t>集成电路设计</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>8.67</t>
+          <t>14.94</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>数据中心</t>
+          <t>其他专用机械</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7.74</t>
+          <t>10.98</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>其他汽车零部件</t>
+          <t>线缆及其他</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7.13</t>
+          <t>9.62</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>其他稀有金属</t>
+          <t>电池部件及材料</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>6.43</t>
+          <t>7.45</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-21.85</t>
+          <t>-7.56</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>建筑装修</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-6.40</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>保险经纪商</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-7.19</t>
+          <t>-6.05</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>化工机械</t>
+          <t>抵押信贷机构</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-6.37</t>
+          <t>-4.63</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>林业产品</t>
+          <t>其他汽车零部件</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-3.45</t>
         </is>
       </c>
     </row>

--- a/每日板块信息自动化分析报告/每日板块信息.xlsx
+++ b/每日板块信息自动化分析报告/每日板块信息.xlsx
@@ -189,25 +189,25 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4055.55</v>
+        <v>4051.43</v>
       </c>
       <c r="D2" t="n">
-        <v>28.34</v>
+        <v>-4.12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7</v>
+        <v>-0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>86.71</v>
+        <v>82.59</v>
       </c>
       <c r="G2" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="H2" t="n">
-        <v>-522.86</v>
+        <v>369.55</v>
       </c>
       <c r="I2" t="n">
-        <v>-5.08</v>
+        <v>3.78</v>
       </c>
     </row>
     <row r="3">
@@ -222,25 +222,25 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>9994.64</v>
+        <v>9928.11</v>
       </c>
       <c r="D3" t="n">
-        <v>49.92</v>
+        <v>-66.53</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>-0.67</v>
       </c>
       <c r="F3" t="n">
-        <v>-21.22</v>
+        <v>-87.75</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.21</v>
+        <v>-0.88</v>
       </c>
       <c r="H3" t="n">
-        <v>-371.36</v>
+        <v>152.37</v>
       </c>
       <c r="I3" t="n">
-        <v>-12.57</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="4">
@@ -255,25 +255,25 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>2939.76</v>
+        <v>2910.87</v>
       </c>
       <c r="D4" t="n">
-        <v>5.55</v>
+        <v>-28.89</v>
       </c>
       <c r="E4" t="n">
-        <v>0.19</v>
+        <v>-0.98</v>
       </c>
       <c r="F4" t="n">
-        <v>-91.36</v>
+        <v>-120.25</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.01</v>
+        <v>-3.97</v>
       </c>
       <c r="H4" t="n">
-        <v>-300.41</v>
+        <v>192.99</v>
       </c>
       <c r="I4" t="n">
-        <v>-20.64</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="5">
@@ -288,25 +288,25 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>4736.61</v>
+        <v>4728.67</v>
       </c>
       <c r="D5" t="n">
-        <v>51.36</v>
+        <v>-7.94</v>
       </c>
       <c r="E5" t="n">
-        <v>1.1</v>
+        <v>-0.17</v>
       </c>
       <c r="F5" t="n">
-        <v>106.67</v>
+        <v>98.73</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3</v>
+        <v>2.13</v>
       </c>
       <c r="H5" t="n">
-        <v>-369.39</v>
+        <v>200.11</v>
       </c>
       <c r="I5" t="n">
-        <v>-6.11</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="6">
@@ -321,25 +321,25 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>7068.81</v>
+        <v>7088.57</v>
       </c>
       <c r="D6" t="n">
-        <v>75.55</v>
+        <v>19.77</v>
       </c>
       <c r="E6" t="n">
-        <v>1.08</v>
+        <v>0.28</v>
       </c>
       <c r="F6" t="n">
-        <v>480.7</v>
+        <v>500.47</v>
       </c>
       <c r="G6" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
       <c r="H6" t="n">
-        <v>-141.43</v>
+        <v>50.14</v>
       </c>
       <c r="I6" t="n">
-        <v>-5.85</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="7">
@@ -354,25 +354,25 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>3237.25</v>
+        <v>3214.51</v>
       </c>
       <c r="D7" t="n">
-        <v>6.27</v>
+        <v>-22.75</v>
       </c>
       <c r="E7" t="n">
-        <v>0.19</v>
+        <v>-0.7</v>
       </c>
       <c r="F7" t="n">
-        <v>199.63</v>
+        <v>176.89</v>
       </c>
       <c r="G7" t="n">
-        <v>6.57</v>
+        <v>5.82</v>
       </c>
       <c r="H7" t="n">
-        <v>-24.15</v>
+        <v>-36.97</v>
       </c>
       <c r="I7" t="n">
-        <v>-7.42</v>
+        <v>-12.28</v>
       </c>
     </row>
     <row r="8">
@@ -387,25 +387,25 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>5734.51</v>
+        <v>5695.32</v>
       </c>
       <c r="D8" t="n">
-        <v>13.92</v>
+        <v>-39.19</v>
       </c>
       <c r="E8" t="n">
-        <v>0.24</v>
+        <v>-0.68</v>
       </c>
       <c r="F8" t="n">
-        <v>230.53</v>
+        <v>191.34</v>
       </c>
       <c r="G8" t="n">
-        <v>4.19</v>
+        <v>3.48</v>
       </c>
       <c r="H8" t="n">
-        <v>-8.75</v>
+        <v>-50.43</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.64</v>
+        <v>-9.63</v>
       </c>
     </row>
     <row r="9">
@@ -420,25 +420,25 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>8180.08</v>
+        <v>8214.19</v>
       </c>
       <c r="D9" t="n">
-        <v>136.0</v>
+        <v>34.11</v>
       </c>
       <c r="E9" t="n">
-        <v>1.69</v>
+        <v>0.42</v>
       </c>
       <c r="F9" t="n">
-        <v>714.51</v>
+        <v>748.62</v>
       </c>
       <c r="G9" t="n">
-        <v>9.57</v>
+        <v>10.03</v>
       </c>
       <c r="H9" t="n">
-        <v>-269.89</v>
+        <v>234.15</v>
       </c>
       <c r="I9" t="n">
-        <v>-5.91</v>
+        <v>5.45</v>
       </c>
     </row>
   </sheetData>
@@ -500,16 +500,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16.54</v>
+        <v>16.51</v>
       </c>
       <c r="C2" t="n">
-        <v>15.81</v>
+        <v>15.79</v>
       </c>
       <c r="D2" t="n">
         <v>1.49</v>
       </c>
       <c r="E2" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="F2" t="n">
         <v>16.21</v>
@@ -528,16 +528,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12.86</v>
+        <v>12.79</v>
       </c>
       <c r="C3" t="n">
-        <v>12.25</v>
+        <v>12.19</v>
       </c>
       <c r="D3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="E3" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="F3" t="n">
         <v>13.03</v>
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.0</v>
+        <v>11.92</v>
       </c>
       <c r="C4" t="n">
-        <v>11.68</v>
+        <v>11.6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="E4" t="n">
-        <v>3.37</v>
+        <v>3.39</v>
       </c>
       <c r="F4" t="n">
         <v>12.33</v>
@@ -584,10 +584,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15.33</v>
+        <v>15.28</v>
       </c>
       <c r="C5" t="n">
-        <v>14.45</v>
+        <v>14.4</v>
       </c>
       <c r="D5" t="n">
         <v>1.46</v>
@@ -612,16 +612,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25.26</v>
+        <v>25.33</v>
       </c>
       <c r="C6" t="n">
-        <v>24.65</v>
+        <v>24.73</v>
       </c>
       <c r="D6" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="E6" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="F6" t="n">
         <v>23.69</v>
@@ -640,16 +640,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8.64</v>
+        <v>8.62</v>
       </c>
       <c r="C7" t="n">
-        <v>8.74</v>
+        <v>8.71</v>
       </c>
       <c r="D7" t="n">
-        <v>0.76</v>
+        <v>0.75</v>
       </c>
       <c r="E7" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="F7" t="n">
         <v>8.62</v>
@@ -668,16 +668,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>8.55</v>
+        <v>8.51</v>
       </c>
       <c r="C8" t="n">
-        <v>8.58</v>
+        <v>8.54</v>
       </c>
       <c r="D8" t="n">
         <v>0.76</v>
       </c>
       <c r="E8" t="n">
-        <v>4.66</v>
+        <v>4.68</v>
       </c>
       <c r="F8" t="n">
         <v>8.62</v>
@@ -696,13 +696,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30.76</v>
+        <v>30.89</v>
       </c>
       <c r="C9" t="n">
-        <v>28.99</v>
+        <v>29.13</v>
       </c>
       <c r="D9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="E9" t="n">
         <v>1.31</v>
@@ -762,22 +762,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>宁德时代</t>
+          <t>新易盛</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>453.98</t>
+          <t>589.00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5.33</t>
+          <t>9.58</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>11.13</t>
+          <t>9.37</t>
         </is>
       </c>
     </row>
@@ -789,22 +789,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>新易盛</t>
+          <t>中际旭创</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>537.50</t>
+          <t>851.00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>5.11</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>7.38</t>
+          <t>8.42</t>
         </is>
       </c>
     </row>
@@ -816,22 +816,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>中际旭创</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>809.61</t>
+          <t>1407.24</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>-6.38</t>
         </is>
       </c>
     </row>
@@ -843,22 +843,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>天孚通信</t>
+          <t>宁德时代</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>355.57</t>
+          <t>444.20</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>-2.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>-4.74</t>
         </is>
       </c>
     </row>
@@ -870,22 +870,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>立讯精密</t>
+          <t>东山精密</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>60.45</t>
+          <t>162.10</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>8.39</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>2.95</t>
         </is>
       </c>
     </row>
@@ -897,22 +897,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>兆易创新</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>286.73</t>
+          <t>99.39</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.65</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>-2.84</t>
         </is>
       </c>
     </row>
@@ -924,22 +924,22 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>蓝思科技</t>
+          <t>胜宏科技</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>25.64</t>
+          <t>326.42</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>-13.35</t>
+          <t>7.55</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>2.56</t>
         </is>
       </c>
     </row>
@@ -951,22 +951,22 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>寒武纪</t>
+          <t>天孚通信</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1307.00</t>
+          <t>379.28</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -978,22 +978,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>比亚迪</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>105.54</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>-1.72</t>
         </is>
       </c>
     </row>
@@ -1005,22 +1005,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>工业富联</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>35.30</t>
+          <t>60.97</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.18</t>
+          <t>1.20</t>
         </is>
       </c>
     </row>
@@ -1032,22 +1032,22 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>协创数据</t>
+          <t>佰维存储</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>319.00</t>
+          <t>270.67</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.65</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>7.36</t>
+          <t>-4.18</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>大族激光</t>
+          <t>光迅科技</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>86.67</t>
+          <t>116.83</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1074,7 +1074,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>5.15</t>
+          <t>4.08</t>
         </is>
       </c>
     </row>
@@ -1086,22 +1086,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>厦门钨业</t>
+          <t>亨通光电</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>61.88</t>
+          <t>55.65</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>10.01</t>
+          <t>4.72</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>3.93</t>
         </is>
       </c>
     </row>
@@ -1113,22 +1113,22 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>长川科技</t>
+          <t>信维通信</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>154.09</t>
+          <t>74.91</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9.12</t>
+          <t>7.32</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>3.92</t>
         </is>
       </c>
     </row>
@@ -1140,22 +1140,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>天华新能</t>
+          <t>中钨高新</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>85.68</t>
+          <t>56.12</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>11.37</t>
+          <t>8.13</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4.04</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
@@ -1167,22 +1167,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>中钨高新</t>
+          <t>杰瑞股份</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>51.90</t>
+          <t>121.18</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>2.38</t>
         </is>
       </c>
     </row>
@@ -1194,22 +1194,22 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>杰瑞股份</t>
+          <t>蓝色光标</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>116.30</t>
+          <t>18.00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>6.23</t>
+          <t>4.65</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>2.28</t>
         </is>
       </c>
     </row>
@@ -1221,22 +1221,22 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>信立泰</t>
+          <t>罗博特科</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>60.54</t>
+          <t>524.00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>-10.00</t>
+          <t>5.55</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>-2.98</t>
+          <t>2.20</t>
         </is>
       </c>
     </row>
@@ -1248,22 +1248,22 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>科达利</t>
+          <t>英维克</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>205.59</t>
+          <t>110.67</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>10.00</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.07</t>
         </is>
       </c>
     </row>
@@ -1275,22 +1275,22 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>中矿资源</t>
+          <t>先导智能</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>85.49</t>
+          <t>56.00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>6.11</t>
+          <t>4.36</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.82</t>
+          <t>2.03</t>
         </is>
       </c>
     </row>
@@ -1302,22 +1302,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>寒武纪</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1307.00</t>
+          <t>1407.24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2.59</t>
+          <t>-3.80</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.26</t>
+          <t>-11.29</t>
         </is>
       </c>
     </row>
@@ -1329,22 +1329,22 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>紫金矿业</t>
+          <t>药明康德</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>35.30</t>
+          <t>99.39</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>-5.03</t>
         </is>
       </c>
     </row>
@@ -1356,22 +1356,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>澜起科技</t>
+          <t>紫金矿业</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>151.00</t>
+          <t>34.73</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>-1.61</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>-3.05</t>
         </is>
       </c>
     </row>
@@ -1383,22 +1383,22 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>中信证券</t>
+          <t>海光信息</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>26.31</t>
+          <t>260.00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>2.11</t>
         </is>
       </c>
     </row>
@@ -1410,22 +1410,22 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>中国平安</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1462.84</t>
+          <t>57.92</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>-2.08</t>
         </is>
       </c>
     </row>
@@ -1437,22 +1437,22 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>药明康德</t>
+          <t>寒武纪</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>105.66</t>
+          <t>1334.00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>1.85</t>
         </is>
       </c>
     </row>
@@ -1464,22 +1464,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>洛阳钼业</t>
+          <t>恒瑞医药</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>20.29</t>
+          <t>56.33</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>-1.98</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-1.65</t>
         </is>
       </c>
     </row>
@@ -1491,22 +1491,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>中国平安</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>58.52</t>
+          <t>39.52</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-0.98</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>-1.57</t>
         </is>
       </c>
     </row>
@@ -1523,17 +1523,17 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>90.10</t>
+          <t>87.77</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>1.15</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>-1.42</t>
         </is>
       </c>
     </row>
@@ -1545,22 +1545,22 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>金山办公</t>
+          <t>兴业银行</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>252.46</t>
+          <t>18.40</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>-1.13</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>-1.15</t>
         </is>
       </c>
     </row>
@@ -1599,12 +1599,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>通信技术服务</t>
+          <t>钛白粉</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>7.83</t>
+          <t>10.01</t>
         </is>
       </c>
     </row>
@@ -1616,12 +1616,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>钨钼</t>
+          <t>铅锌</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>7.12</t>
+          <t>6.17</t>
         </is>
       </c>
     </row>
@@ -1633,12 +1633,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>其他发电设备</t>
+          <t>膜材料</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>5.67</t>
+          <t>5.90</t>
         </is>
       </c>
     </row>
@@ -1650,12 +1650,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>云计算服务</t>
+          <t>光学元件</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>5.85</t>
         </is>
       </c>
     </row>
@@ -1667,12 +1667,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>钴镍</t>
+          <t>LED</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4.66</t>
+          <t>5.09</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.17</t>
+          <t>-4.30</t>
         </is>
       </c>
     </row>
@@ -1701,12 +1701,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>航运</t>
+          <t>环境监测</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.10</t>
+          <t>-3.84</t>
         </is>
       </c>
     </row>
@@ -1718,12 +1718,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>黑色家电</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>-3.47</t>
         </is>
       </c>
     </row>
@@ -1735,12 +1735,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>固废处理</t>
+          <t>锦纶与涤纶</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.03</t>
+          <t>-2.99</t>
         </is>
       </c>
     </row>
@@ -1752,12 +1752,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>医药商业</t>
+          <t>天然气加工</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.02</t>
+          <t>-2.98</t>
         </is>
       </c>
     </row>
@@ -1769,12 +1769,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>集成电路设计</t>
+          <t>集成电路制造</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>16.51</t>
+          <t>6.37</t>
         </is>
       </c>
     </row>
@@ -1786,12 +1786,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>市政环卫</t>
+          <t>通信系统设备及组件</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>5.79</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>摩托车及其他</t>
+          <t>中药饮片</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>7.07</t>
+          <t>5.73</t>
         </is>
       </c>
     </row>
@@ -1820,12 +1820,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>钨钼</t>
+          <t>市政环卫</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6.98</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -1837,12 +1837,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>其他钢铁</t>
+          <t>印制电路板</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6.76</t>
+          <t>5.12</t>
         </is>
       </c>
     </row>
@@ -1854,12 +1854,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>工程机械</t>
+          <t>酒店</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>-4.71</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>药品制剂</t>
+          <t>云计算服务</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>-3.32</t>
         </is>
       </c>
     </row>
@@ -1888,12 +1888,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>航天</t>
+          <t>旅游服务</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.15</t>
+          <t>-2.99</t>
         </is>
       </c>
     </row>
@@ -1905,12 +1905,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>氨纶及其他化纤</t>
+          <t>锦纶与涤纶</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-1.13</t>
+          <t>-2.66</t>
         </is>
       </c>
     </row>
@@ -1922,12 +1922,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>综合性银行</t>
+          <t>商用车</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-2.60</t>
         </is>
       </c>
     </row>
@@ -1939,12 +1939,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>其他储能设备</t>
+          <t>行业应用软件</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>36.19</t>
         </is>
       </c>
     </row>
@@ -1956,12 +1956,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>集成电路设计</t>
+          <t>线缆及其他</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>6.70</t>
         </is>
       </c>
     </row>
@@ -1973,12 +1973,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>其他专用机械</t>
+          <t>铅锌</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>10.98</t>
+          <t>6.61</t>
         </is>
       </c>
     </row>
@@ -1990,12 +1990,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>线缆及其他</t>
+          <t>其他综合性金融服务</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>9.62</t>
+          <t>5.73</t>
         </is>
       </c>
     </row>
@@ -2007,12 +2007,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>电池部件及材料</t>
+          <t>其他专用机械</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>7.45</t>
+          <t>5.37</t>
         </is>
       </c>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>纺织服装机械</t>
+          <t>其他储能设备</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>-7.56</t>
+          <t>-10.84</t>
         </is>
       </c>
     </row>
@@ -2041,12 +2041,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LED</t>
+          <t>市政环卫</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>-6.40</t>
+          <t>-4.45</t>
         </is>
       </c>
     </row>
@@ -2058,12 +2058,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>保险经纪商</t>
+          <t>钨钼</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>-6.05</t>
+          <t>-4.25</t>
         </is>
       </c>
     </row>
@@ -2075,12 +2075,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>抵押信贷机构</t>
+          <t>气液机械</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-4.07</t>
         </is>
       </c>
     </row>
@@ -2092,12 +2092,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>其他汽车零部件</t>
+          <t>畜牧产品</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>-3.45</t>
+          <t>-4.00</t>
         </is>
       </c>
     </row>
